--- a/DataTables/Datas/dialogcontent.xlsx
+++ b/DataTables/Datas/dialogcontent.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\Hippo-s-Epic\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11F19BBF-9894-47DE-868A-367CAE5CD6E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D045F4B0-A41E-4B1D-A9B7-767F880A7DC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="136">
   <si>
     <t>##var</t>
   </si>
@@ -443,6 +443,14 @@
   </si>
   <si>
     <t>我们不是还他妈的有这盏灯吗？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>巴拉巴拉，无论如何，去拳击馆</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>好吧。</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -852,7 +860,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S93"/>
+  <dimension ref="A1:S95"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="12.125" style="9" customWidth="1"/>
@@ -3621,6 +3629,58 @@
         <v>0</v>
       </c>
     </row>
+    <row r="94" spans="2:18" s="7" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="B94" s="7">
+        <v>91</v>
+      </c>
+      <c r="C94" s="7">
+        <v>1005001</v>
+      </c>
+      <c r="D94" s="7">
+        <v>2</v>
+      </c>
+      <c r="E94" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="G94" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="H94" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="I94" s="7">
+        <v>0</v>
+      </c>
+      <c r="J94" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="2:18" s="7" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="B95" s="7">
+        <v>92</v>
+      </c>
+      <c r="C95" s="7">
+        <v>1005001</v>
+      </c>
+      <c r="D95" s="7">
+        <v>1</v>
+      </c>
+      <c r="E95" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="G95" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="H95" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="I95" s="7">
+        <v>0</v>
+      </c>
+      <c r="J95" s="7">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/DataTables/Datas/dialogcontent.xlsx
+++ b/DataTables/Datas/dialogcontent.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\Hippo-s-Epic\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D045F4B0-A41E-4B1D-A9B7-767F880A7DC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19489AFC-DAC8-4A71-876D-C25DE1734CA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="137">
   <si>
     <t>##var</t>
   </si>
@@ -451,6 +451,10 @@
   </si>
   <si>
     <t>好吧。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>拿牙或者随便找个人上去打一架，让比赛重新开起来。</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -860,7 +864,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S95"/>
+  <dimension ref="A1:S97"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="12.125" style="9" customWidth="1"/>
@@ -3681,6 +3685,58 @@
         <v>0</v>
       </c>
     </row>
+    <row r="96" spans="2:18" s="12" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="B96" s="12">
+        <v>93</v>
+      </c>
+      <c r="C96" s="12">
+        <v>1006001</v>
+      </c>
+      <c r="D96" s="12">
+        <v>2</v>
+      </c>
+      <c r="E96" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="G96" s="14" t="s">
+        <v>122</v>
+      </c>
+      <c r="H96" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="I96" s="12">
+        <v>0</v>
+      </c>
+      <c r="J96" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="2:10" s="12" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="B97" s="12">
+        <v>94</v>
+      </c>
+      <c r="C97" s="12">
+        <v>1006001</v>
+      </c>
+      <c r="D97" s="12">
+        <v>1</v>
+      </c>
+      <c r="E97" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="G97" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="H97" s="14" t="s">
+        <v>122</v>
+      </c>
+      <c r="I97" s="12">
+        <v>0</v>
+      </c>
+      <c r="J97" s="12">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/DataTables/Datas/dialogcontent.xlsx
+++ b/DataTables/Datas/dialogcontent.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\Hippo-s-Epic\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19489AFC-DAC8-4A71-876D-C25DE1734CA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EB9F5C8-44E8-4028-8F6C-C3132CF36498}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="144">
   <si>
     <t>##var</t>
   </si>
@@ -455,6 +455,34 @@
   </si>
   <si>
     <t>拿牙或者随便找个人上去打一架，让比赛重新开起来。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>回来了？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>我什么都没拿到</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>我找到牙了</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>你个废物，快去找</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>好，那比赛可以开起来了</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>我找到了这份报道</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>天哪，燃起了我心中的一团火，我要上去揍人了</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -494,7 +522,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -504,6 +532,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -520,7 +554,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -560,6 +594,15 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -864,7 +907,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S97"/>
+  <dimension ref="A1:S104"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="12.125" style="9" customWidth="1"/>
@@ -3296,7 +3339,9 @@
       <c r="E82" s="13" t="s">
         <v>127</v>
       </c>
-      <c r="F82" s="11"/>
+      <c r="F82" s="7">
+        <v>1</v>
+      </c>
       <c r="G82" s="14" t="s">
         <v>122</v>
       </c>
@@ -3333,7 +3378,9 @@
       <c r="E83" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="F83" s="11"/>
+      <c r="F83" s="7">
+        <v>2</v>
+      </c>
       <c r="G83" s="14" t="s">
         <v>122</v>
       </c>
@@ -3368,7 +3415,9 @@
       <c r="E84" s="13" t="s">
         <v>128</v>
       </c>
-      <c r="F84" s="11"/>
+      <c r="F84" s="7">
+        <v>3</v>
+      </c>
       <c r="G84" s="14" t="s">
         <v>122</v>
       </c>
@@ -3403,7 +3452,9 @@
       <c r="E85" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="F85" s="11"/>
+      <c r="F85" s="7">
+        <v>4</v>
+      </c>
       <c r="G85" s="14" t="s">
         <v>122</v>
       </c>
@@ -3438,6 +3489,9 @@
       <c r="E86" s="6" t="s">
         <v>129</v>
       </c>
+      <c r="F86" s="7">
+        <v>5</v>
+      </c>
       <c r="G86" s="2" t="s">
         <v>125</v>
       </c>
@@ -3464,6 +3518,9 @@
       <c r="E87" s="6" t="s">
         <v>123</v>
       </c>
+      <c r="F87" s="7">
+        <v>6</v>
+      </c>
       <c r="G87" s="2" t="s">
         <v>121</v>
       </c>
@@ -3490,6 +3547,9 @@
       <c r="E88" s="6" t="s">
         <v>130</v>
       </c>
+      <c r="F88" s="7">
+        <v>7</v>
+      </c>
       <c r="G88" s="2" t="s">
         <v>121</v>
       </c>
@@ -3516,6 +3576,9 @@
       <c r="E89" s="6" t="s">
         <v>131</v>
       </c>
+      <c r="F89" s="7">
+        <v>8</v>
+      </c>
       <c r="G89" s="2" t="s">
         <v>122</v>
       </c>
@@ -3542,6 +3605,9 @@
       <c r="E90" s="6" t="s">
         <v>132</v>
       </c>
+      <c r="F90" s="7">
+        <v>9</v>
+      </c>
       <c r="G90" s="2" t="s">
         <v>122</v>
       </c>
@@ -3568,6 +3634,9 @@
       <c r="E91" s="6" t="s">
         <v>133</v>
       </c>
+      <c r="F91" s="7">
+        <v>10</v>
+      </c>
       <c r="G91" s="2" t="s">
         <v>121</v>
       </c>
@@ -3594,6 +3663,9 @@
       <c r="E92" s="6" t="s">
         <v>124</v>
       </c>
+      <c r="F92" s="7">
+        <v>11</v>
+      </c>
       <c r="G92" s="2" t="s">
         <v>122</v>
       </c>
@@ -3620,6 +3692,9 @@
       <c r="E93" s="6" t="s">
         <v>124</v>
       </c>
+      <c r="F93" s="7">
+        <v>12</v>
+      </c>
       <c r="G93" s="2" t="s">
         <v>122</v>
       </c>
@@ -3646,6 +3721,9 @@
       <c r="E94" s="8" t="s">
         <v>134</v>
       </c>
+      <c r="F94" s="7">
+        <v>1</v>
+      </c>
       <c r="G94" s="10" t="s">
         <v>122</v>
       </c>
@@ -3672,6 +3750,9 @@
       <c r="E95" s="8" t="s">
         <v>135</v>
       </c>
+      <c r="F95" s="7">
+        <v>2</v>
+      </c>
       <c r="G95" s="10" t="s">
         <v>121</v>
       </c>
@@ -3698,6 +3779,9 @@
       <c r="E96" s="13" t="s">
         <v>136</v>
       </c>
+      <c r="F96" s="12">
+        <v>1</v>
+      </c>
       <c r="G96" s="14" t="s">
         <v>122</v>
       </c>
@@ -3724,6 +3808,9 @@
       <c r="E97" s="13" t="s">
         <v>135</v>
       </c>
+      <c r="F97" s="12">
+        <v>2</v>
+      </c>
       <c r="G97" s="14" t="s">
         <v>121</v>
       </c>
@@ -3734,6 +3821,209 @@
         <v>0</v>
       </c>
       <c r="J97" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="2:10" s="15" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="B98" s="15">
+        <v>95</v>
+      </c>
+      <c r="C98" s="15">
+        <v>1007001</v>
+      </c>
+      <c r="D98" s="15">
+        <v>2</v>
+      </c>
+      <c r="E98" s="16" t="s">
+        <v>137</v>
+      </c>
+      <c r="F98" s="15">
+        <v>1</v>
+      </c>
+      <c r="G98" s="17" t="s">
+        <v>121</v>
+      </c>
+      <c r="H98" s="17" t="s">
+        <v>122</v>
+      </c>
+      <c r="I98" s="15">
+        <v>0</v>
+      </c>
+      <c r="J98" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="2:10" s="7" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="B99" s="12">
+        <v>96</v>
+      </c>
+      <c r="C99" s="7">
+        <v>1007003</v>
+      </c>
+      <c r="D99" s="7">
+        <v>1</v>
+      </c>
+      <c r="E99" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="F99" s="7">
+        <v>1</v>
+      </c>
+      <c r="G99" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="H99" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="I99" s="7">
+        <v>0</v>
+      </c>
+      <c r="J99" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="2:10" s="7" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="B100" s="12">
+        <v>97</v>
+      </c>
+      <c r="C100" s="7">
+        <v>1007003</v>
+      </c>
+      <c r="D100" s="7">
+        <v>2</v>
+      </c>
+      <c r="E100" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="F100" s="7">
+        <v>2</v>
+      </c>
+      <c r="G100" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="H100" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="I100" s="7">
+        <v>0</v>
+      </c>
+      <c r="J100" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="2:10" s="12" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="B101" s="12">
+        <v>98</v>
+      </c>
+      <c r="C101" s="12">
+        <v>1007004</v>
+      </c>
+      <c r="D101" s="12">
+        <v>1</v>
+      </c>
+      <c r="E101" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="F101" s="12">
+        <v>1</v>
+      </c>
+      <c r="G101" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="H101" s="14" t="s">
+        <v>122</v>
+      </c>
+      <c r="I101" s="12">
+        <v>0</v>
+      </c>
+      <c r="J101" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="2:10" s="12" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="B102" s="12">
+        <v>99</v>
+      </c>
+      <c r="C102" s="12">
+        <v>1007004</v>
+      </c>
+      <c r="D102" s="12">
+        <v>2</v>
+      </c>
+      <c r="E102" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="F102" s="12">
+        <v>2</v>
+      </c>
+      <c r="G102" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="H102" s="14" t="s">
+        <v>122</v>
+      </c>
+      <c r="I102" s="12">
+        <v>0</v>
+      </c>
+      <c r="J102" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="2:10" s="7" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="B103" s="12">
+        <v>100</v>
+      </c>
+      <c r="C103" s="7">
+        <v>1007005</v>
+      </c>
+      <c r="D103" s="7">
+        <v>1</v>
+      </c>
+      <c r="E103" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="F103" s="7">
+        <v>1</v>
+      </c>
+      <c r="G103" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="H103" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="I103" s="7">
+        <v>0</v>
+      </c>
+      <c r="J103" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="2:10" s="7" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="B104" s="12">
+        <v>101</v>
+      </c>
+      <c r="C104" s="7">
+        <v>1007005</v>
+      </c>
+      <c r="D104" s="7">
+        <v>2</v>
+      </c>
+      <c r="E104" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="F104" s="7">
+        <v>2</v>
+      </c>
+      <c r="G104" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="H104" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="I104" s="7">
+        <v>0</v>
+      </c>
+      <c r="J104" s="7">
         <v>0</v>
       </c>
     </row>

--- a/DataTables/Datas/dialogcontent.xlsx
+++ b/DataTables/Datas/dialogcontent.xlsx
@@ -496,7 +496,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T105"/>
+  <dimension ref="A1:T107"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="12.125" customWidth="1" style="12" min="1" max="1"/>
@@ -4646,6 +4646,70 @@
         <v>1</v>
       </c>
     </row>
+    <row r="106">
+      <c r="B106" t="n">
+        <v>103</v>
+      </c>
+      <c r="C106" t="n">
+        <v>9001002</v>
+      </c>
+      <c r="D106" t="n">
+        <v>0</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>【测试】要现在打一场吗？</t>
+        </is>
+      </c>
+      <c r="F106" t="n">
+        <v>1</v>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>idle</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>idle</t>
+        </is>
+      </c>
+      <c r="S106" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="B107" t="n">
+        <v>104</v>
+      </c>
+      <c r="C107" t="n">
+        <v>9001004</v>
+      </c>
+      <c r="D107" t="n">
+        <v>0</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>【测试】好的，那就算了。</t>
+        </is>
+      </c>
+      <c r="F107" t="n">
+        <v>1</v>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>idle</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>idle</t>
+        </is>
+      </c>
+      <c r="S107" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
